--- a/KatalonData/RADTestData/BeforePaymentsCorp.xlsx
+++ b/KatalonData/RADTestData/BeforePaymentsCorp.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="510">
   <si>
     <t>Result</t>
   </si>
@@ -717,12 +717,871 @@
   </si>
   <si>
     <t>Sun Aug 02 21:36:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:31:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:33:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:35:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:36:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:37:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:38:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:39:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:40:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:41:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:43:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:44:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:45:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:46:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:47:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:48:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:49:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:50:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:50:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:51:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:52:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:54:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:54:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:55:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:57:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:58:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 19:59:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:00:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:01:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:01:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:03:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:04:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:05:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:06:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:07:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:08:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:09:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:10:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:12:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:13:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:14:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:15:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:16:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:17:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:17:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:18:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:19:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:20:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:21:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:22:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:23:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:24:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:25:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:26:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:27:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:28:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:29:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:29:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:31:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:31:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:32:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:33:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:34:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:35:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:36:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:37:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:38:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:39:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:40:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:41:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:42:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:43:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:44:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:45:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:46:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:46:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:47:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:48:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:49:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:50:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:51:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:52:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:53:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:54:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:55:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:56:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:57:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:58:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 20:59:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:00:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:01:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:02:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:03:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:04:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:05:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:06:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:07:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:08:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:09:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:10:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:11:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:11:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:12:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:13:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:14:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:15:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:16:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:17:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:18:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:19:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:20:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:22:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:23:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:24:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:25:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:25:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:26:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:27:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:28:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:29:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:30:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:31:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:32:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:33:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:34:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:35:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:36:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:37:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:38:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:39:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:40:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:41:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:42:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:43:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:44:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:45:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:46:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:47:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:48:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:49:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:50:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:51:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:52:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:53:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:54:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:54:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:55:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:56:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:58:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 21:59:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:00:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:01:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:02:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:03:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:04:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:05:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:06:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:07:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:08:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:09:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:10:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:11:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:12:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:13:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:14:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:15:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:16:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:17:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:18:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:19:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:20:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:21:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:22:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:23:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:24:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:25:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:26:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:27:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:28:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:29:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:30:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:31:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:32:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:33:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:34:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:35:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:36:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:37:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:39:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:40:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:41:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:42:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:43:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:44:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:45:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:46:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:47:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:48:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:48:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:49:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:50:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:51:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:52:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:53:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:54:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:56:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:57:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:58:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 22:59:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:01:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:03:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:04:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:05:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:06:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:07:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:08:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:09:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:11:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:12:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:13:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:14:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:15:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:16:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:17:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:18:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:19:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:20:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:21:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:22:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:23:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:24:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:25:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:26:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:27:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:28:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:29:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:30:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:31:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:32:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:33:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:34:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:34:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:35:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:36:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:37:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:38:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:39:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:40:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:41:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:42:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:43:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:44:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:45:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:46:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:47:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:48:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:49:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:50:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:51:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:52:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:53:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:54:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:55:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:56:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:57:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:58:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 23:59:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:00:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:01:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:02:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:04:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:04:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:05:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:06:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:07:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:08:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:09:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:11:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:11:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:12:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:13:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:14:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:15:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:16:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:17:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 16 00:18:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 21:41:12 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1095,17 +1954,17 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1145,7 +2004,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>224</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1174,7 +2033,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1203,7 +2062,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>120</v>
+        <v>226</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1235,7 +2094,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>121</v>
+        <v>227</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1267,7 +2126,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>122</v>
+        <v>228</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1299,7 +2158,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>123</v>
+        <v>229</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1331,7 +2190,7 @@
         <v>115</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1364,16 +2223,16 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1413,7 +2272,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>125</v>
+        <v>231</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1436,7 +2295,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>232</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1459,7 +2318,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>127</v>
+        <v>233</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1482,7 +2341,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>128</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1508,7 +2367,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>129</v>
+        <v>235</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1534,7 +2393,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>130</v>
+        <v>236</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1557,7 +2416,7 @@
         <v>115</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>131</v>
+        <v>237</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1580,7 +2439,7 @@
         <v>115</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>132</v>
+        <v>238</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -1603,7 +2462,7 @@
         <v>115</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>133</v>
+        <v>239</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -1626,7 +2485,7 @@
         <v>115</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>134</v>
+        <v>240</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -1649,7 +2508,7 @@
         <v>115</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>135</v>
+        <v>241</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -1672,7 +2531,7 @@
         <v>115</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>136</v>
+        <v>242</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -1695,7 +2554,7 @@
         <v>115</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -1718,7 +2577,7 @@
         <v>115</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>138</v>
+        <v>244</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -1738,7 +2597,7 @@
         <v>115</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>139</v>
+        <v>245</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -1764,7 +2623,7 @@
         <v>115</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>140</v>
+        <v>246</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -1787,7 +2646,7 @@
         <v>115</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>141</v>
+        <v>247</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -1827,7 +2686,7 @@
         <v>115</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>142</v>
+        <v>248</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -1872,15 +2731,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1917,7 +2776,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>143</v>
+        <v>249</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1943,7 +2802,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1966,7 +2825,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>145</v>
+        <v>251</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1992,7 +2851,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>146</v>
+        <v>252</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2018,7 +2877,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>147</v>
+        <v>253</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2044,7 +2903,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>148</v>
+        <v>254</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2079,17 +2938,17 @@
   <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="19.796875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.19921875" style="1" collapsed="1"/>
-    <col min="13" max="13" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="1" width="19.796875"/>
+    <col min="12" max="12" style="1" width="9.19921875" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
+    <col min="14" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
@@ -2138,7 +2997,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>149</v>
+        <v>435</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2161,7 +3020,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>150</v>
+        <v>436</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2187,7 +3046,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>151</v>
+        <v>437</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2213,7 +3072,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>152</v>
+        <v>438</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2239,7 +3098,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>153</v>
+        <v>439</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2265,7 +3124,7 @@
         <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>154</v>
+        <v>440</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2288,7 +3147,7 @@
         <v>115</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>155</v>
+        <v>441</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -2314,7 +3173,7 @@
         <v>115</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>156</v>
+        <v>442</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -2340,7 +3199,7 @@
         <v>115</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>157</v>
+        <v>443</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -2366,7 +3225,7 @@
         <v>115</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>158</v>
+        <v>444</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -2392,7 +3251,7 @@
         <v>115</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>159</v>
+        <v>445</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -2415,7 +3274,7 @@
         <v>115</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>160</v>
+        <v>446</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -2441,7 +3300,7 @@
         <v>115</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>161</v>
+        <v>447</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -2467,7 +3326,7 @@
         <v>115</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>162</v>
+        <v>448</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -2493,7 +3352,7 @@
         <v>115</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>163</v>
+        <v>449</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -2519,7 +3378,7 @@
         <v>115</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>164</v>
+        <v>450</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -2548,7 +3407,7 @@
         <v>115</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>165</v>
+        <v>451</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -2577,7 +3436,7 @@
         <v>115</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>166</v>
+        <v>452</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
@@ -2606,7 +3465,7 @@
         <v>115</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>167</v>
+        <v>453</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -2629,7 +3488,7 @@
         <v>115</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>168</v>
+        <v>454</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
@@ -2658,7 +3517,7 @@
         <v>115</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>169</v>
+        <v>455</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>29</v>
@@ -2687,7 +3546,7 @@
         <v>115</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>170</v>
+        <v>456</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
@@ -2713,7 +3572,7 @@
         <v>115</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>171</v>
+        <v>457</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
@@ -2742,7 +3601,7 @@
         <v>115</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>172</v>
+        <v>458</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
@@ -2774,7 +3633,7 @@
         <v>115</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>173</v>
+        <v>459</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
@@ -2803,7 +3662,7 @@
         <v>115</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>174</v>
+        <v>460</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>29</v>
@@ -2832,7 +3691,7 @@
         <v>115</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>175</v>
+        <v>461</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>29</v>
@@ -2864,7 +3723,7 @@
         <v>115</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>176</v>
+        <v>462</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>29</v>
@@ -2893,7 +3752,7 @@
         <v>115</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>177</v>
+        <v>463</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>29</v>
@@ -2922,7 +3781,7 @@
         <v>115</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>178</v>
+        <v>464</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>29</v>
@@ -2951,7 +3810,7 @@
         <v>115</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>179</v>
+        <v>465</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
@@ -2974,7 +3833,7 @@
         <v>115</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>180</v>
+        <v>466</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>29</v>
@@ -3003,7 +3862,7 @@
         <v>115</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>181</v>
+        <v>467</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>29</v>
@@ -3032,7 +3891,7 @@
         <v>115</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>182</v>
+        <v>468</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>29</v>
@@ -3058,7 +3917,7 @@
         <v>115</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>183</v>
+        <v>469</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
@@ -3087,7 +3946,7 @@
         <v>115</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>184</v>
+        <v>470</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>29</v>
@@ -3119,7 +3978,7 @@
         <v>115</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>185</v>
+        <v>471</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>29</v>
@@ -3148,7 +4007,7 @@
         <v>115</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>186</v>
+        <v>472</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
@@ -3177,7 +4036,7 @@
         <v>115</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>187</v>
+        <v>473</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
@@ -3209,7 +4068,7 @@
         <v>115</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>188</v>
+        <v>474</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
@@ -3238,7 +4097,7 @@
         <v>115</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>189</v>
+        <v>475</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
@@ -3267,7 +4126,7 @@
         <v>115</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>190</v>
+        <v>476</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
@@ -3296,7 +4155,7 @@
         <v>115</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>191</v>
+        <v>477</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
@@ -3319,7 +4178,7 @@
         <v>115</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>192</v>
+        <v>478</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>29</v>
@@ -3348,7 +4207,7 @@
         <v>115</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>193</v>
+        <v>479</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
@@ -3377,7 +4236,7 @@
         <v>115</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>194</v>
+        <v>480</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>29</v>
@@ -3403,7 +4262,7 @@
         <v>115</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>195</v>
+        <v>481</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>29</v>
@@ -3432,7 +4291,7 @@
         <v>115</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>196</v>
+        <v>482</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>29</v>
@@ -3464,7 +4323,7 @@
         <v>115</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>197</v>
+        <v>483</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>29</v>
@@ -3493,7 +4352,7 @@
         <v>115</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>198</v>
+        <v>484</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>29</v>
@@ -3522,7 +4381,7 @@
         <v>115</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>199</v>
+        <v>485</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>29</v>
@@ -3554,7 +4413,7 @@
         <v>115</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>200</v>
+        <v>486</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>29</v>
@@ -3574,10 +4433,10 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>218</v>
+        <v>487</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>29</v>
@@ -3623,7 +4482,7 @@
         <v>115</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>201</v>
+        <v>488</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>29</v>
@@ -3643,10 +4502,10 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A57" s="1" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>219</v>
+        <v>509</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>29</v>
@@ -3692,7 +4551,7 @@
         <v>115</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>202</v>
+        <v>490</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>29</v>
@@ -3715,7 +4574,7 @@
         <v>115</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>220</v>
+        <v>491</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>29</v>
@@ -3761,7 +4620,7 @@
         <v>115</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>203</v>
+        <v>492</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>29</v>
@@ -3787,7 +4646,7 @@
         <v>115</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>204</v>
+        <v>493</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>29</v>
@@ -3813,7 +4672,7 @@
         <v>115</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>205</v>
+        <v>494</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>29</v>
@@ -3849,14 +4708,14 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -3890,7 +4749,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>207</v>
+        <v>496</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -3913,7 +4772,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>208</v>
+        <v>497</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -3936,7 +4795,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>209</v>
+        <v>498</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -3959,7 +4818,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>210</v>
+        <v>499</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -3982,7 +4841,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>211</v>
+        <v>500</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4002,10 +4861,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>221</v>
+        <v>501</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -4022,10 +4881,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>222</v>
+        <v>502</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -4044,8 +4903,8 @@
       <c r="A9" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B9" t="s">
-        <v>223</v>
+      <c r="B9" t="s" s="1">
+        <v>503</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -4070,14 +4929,14 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
+    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -4108,7 +4967,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>212</v>
+        <v>504</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4131,7 +4990,7 @@
         <v>115</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>213</v>
+        <v>505</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -4154,7 +5013,7 @@
         <v>115</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>214</v>
+        <v>506</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -4177,7 +5036,7 @@
         <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>215</v>
+        <v>507</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -4200,7 +5059,7 @@
         <v>115</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>216</v>
+        <v>508</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4228,12 +5087,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4261,7 +5120,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>206</v>
+        <v>495</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
